--- a/metadata/nomenclature_mapping_and_timing.xlsx
+++ b/metadata/nomenclature_mapping_and_timing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://stevens0-my.sharepoint.com/personal/afaubert_stevens_edu/Documents/Shanglab/follicular_curvature_Kohei/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="13_ncr:1_{A42DBF71-F9E4-4309-85B5-8E465D1F6952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC07B51A-4676-47A8-80A1-EBE429EDECBA}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{A42DBF71-F9E4-4309-85B5-8E465D1F6952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46FC2D25-6BB7-48AC-B0D0-DCBBDFCA2644}"/>
   <bookViews>
-    <workbookView xWindow="11655" yWindow="4740" windowWidth="17280" windowHeight="8880" xr2:uid="{E27DE84C-5FD2-4830-9478-165253811CBF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E27DE84C-5FD2-4830-9478-165253811CBF}"/>
   </bookViews>
   <sheets>
     <sheet name="Follicles" sheetId="4" r:id="rId1"/>
@@ -205,7 +205,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -216,12 +216,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -683,19 +677,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D856B9F7-19F9-44BC-9EF8-EC8B07716C1C}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
-    <col min="2" max="2" width="17.5703125" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" customWidth="1"/>
+    <col min="1" max="1" width="11.109375" customWidth="1"/>
+    <col min="2" max="2" width="17.5546875" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
-    <col min="5" max="6" width="19.42578125" customWidth="1"/>
-    <col min="7" max="7" width="21.85546875" customWidth="1"/>
-    <col min="8" max="8" width="17.7109375" customWidth="1"/>
-    <col min="9" max="9" width="68.7109375" customWidth="1"/>
+    <col min="5" max="6" width="19.44140625" customWidth="1"/>
+    <col min="7" max="7" width="21.88671875" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="68.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>31</v>
       </c>
@@ -724,7 +718,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="b">
         <v>1</v>
       </c>
@@ -743,7 +737,7 @@
       <c r="F2" s="1">
         <v>61</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="1">
         <v>71</v>
       </c>
       <c r="H2" t="s">
@@ -753,7 +747,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="b">
         <v>1</v>
       </c>
@@ -761,19 +755,19 @@
         <v>1</v>
       </c>
       <c r="C3" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3" s="1">
-        <v>9</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>35</v>
+        <v>6</v>
+      </c>
+      <c r="E3" s="1">
+        <v>159</v>
       </c>
       <c r="F3" s="1">
-        <v>8</v>
-      </c>
-      <c r="G3" s="5">
-        <v>14</v>
+        <v>168</v>
+      </c>
+      <c r="G3" s="1">
+        <v>180</v>
       </c>
       <c r="H3" t="s">
         <v>21</v>
@@ -782,330 +776,330 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="b">
         <v>1</v>
       </c>
       <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
         <v>3</v>
       </c>
+      <c r="C4" s="1"/>
       <c r="D4" s="1">
         <v>6</v>
       </c>
       <c r="E4" s="1">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="F4" s="1">
-        <v>168</v>
-      </c>
-      <c r="G4" s="5">
-        <v>180</v>
+        <v>101</v>
+      </c>
+      <c r="G4" s="1">
+        <v>114</v>
       </c>
       <c r="H4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="b">
         <v>1</v>
       </c>
       <c r="B5" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
+        <v>7</v>
+      </c>
+      <c r="E5" s="1">
+        <v>239</v>
+      </c>
+      <c r="F5" s="1">
+        <v>249</v>
+      </c>
+      <c r="G5" s="1">
+        <v>260</v>
+      </c>
+      <c r="H5" t="s">
+        <v>25</v>
+      </c>
+      <c r="I5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" t="b">
+        <v>1</v>
+      </c>
+      <c r="B6" s="1">
         <v>6</v>
-      </c>
-      <c r="E5" s="1">
-        <v>21</v>
-      </c>
-      <c r="F5" s="1">
-        <v>101</v>
-      </c>
-      <c r="G5" s="5">
-        <v>114</v>
-      </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" t="b">
-        <v>1</v>
-      </c>
-      <c r="B6" s="1">
-        <v>4</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
+        <v>8</v>
+      </c>
+      <c r="E6" s="1">
+        <v>166</v>
+      </c>
+      <c r="F6" s="1">
+        <v>211</v>
+      </c>
+      <c r="G6" s="1">
+        <v>219</v>
+      </c>
+      <c r="H6" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" t="b">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1">
         <v>7</v>
       </c>
-      <c r="E6" s="1">
-        <v>239</v>
-      </c>
-      <c r="F6" s="1">
-        <v>249</v>
-      </c>
-      <c r="G6" s="5">
-        <v>260</v>
-      </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="B7" s="2">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1">
         <v>4</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2">
-        <v>10</v>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="E7" s="1">
+        <v>115</v>
+      </c>
+      <c r="F7" s="1">
+        <v>122</v>
+      </c>
+      <c r="G7" s="1">
+        <v>156</v>
+      </c>
+      <c r="H7" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="b">
         <v>1</v>
       </c>
       <c r="B8" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C8" s="1"/>
       <c r="D8" s="1">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="E8" s="1">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="F8" s="1">
-        <v>211</v>
-      </c>
-      <c r="G8" s="5">
-        <v>219</v>
+        <v>199</v>
+      </c>
+      <c r="G8" s="1">
+        <v>215</v>
       </c>
       <c r="H8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="I8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" t="b">
-        <v>1</v>
-      </c>
-      <c r="B9" s="1">
-        <v>7</v>
-      </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1">
-        <v>4</v>
-      </c>
-      <c r="E9" s="1">
-        <v>115</v>
-      </c>
-      <c r="F9" s="1">
-        <v>122</v>
-      </c>
-      <c r="G9" s="5">
-        <v>156</v>
-      </c>
-      <c r="H9" t="s">
-        <v>22</v>
-      </c>
-      <c r="I9" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" t="b">
-        <v>1</v>
-      </c>
-      <c r="B10" s="1">
-        <v>8</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2">
+        <v>9</v>
+      </c>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="1">
-        <v>158</v>
-      </c>
-      <c r="F10" s="1">
-        <v>199</v>
-      </c>
-      <c r="G10" s="5">
-        <v>215</v>
-      </c>
-      <c r="H10" t="s">
-        <v>24</v>
-      </c>
-      <c r="I10" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" t="b">
-        <v>1</v>
-      </c>
-      <c r="B11" s="1">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1">
-        <v>9</v>
-      </c>
-      <c r="F11" s="1">
-        <v>32</v>
-      </c>
-      <c r="G11" s="5">
-        <v>41</v>
-      </c>
-      <c r="H11" t="s">
-        <v>26</v>
-      </c>
-      <c r="I11" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="b">
         <v>0</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="3" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="b">
         <v>0</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
       <c r="H13" s="3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="b">
         <v>0</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="3" t="s">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="B15" s="2"/>
+      <c r="B15" s="2">
+        <v>4</v>
+      </c>
       <c r="C15" s="2"/>
       <c r="D15" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="3" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="b">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" t="b">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1">
+        <v>2</v>
+      </c>
+      <c r="D16" s="1">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="1">
+        <v>8</v>
+      </c>
+      <c r="G16" s="1">
+        <v>14</v>
+      </c>
+      <c r="H16" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" t="b">
+        <v>1</v>
+      </c>
+      <c r="B17" s="1">
+        <v>9</v>
+      </c>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1">
         <v>0</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2">
-        <v>7</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2">
-        <v>4</v>
-      </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>13</v>
+      <c r="E17" s="1">
+        <v>9</v>
+      </c>
+      <c r="F17" s="1">
+        <v>32</v>
+      </c>
+      <c r="G17" s="1">
+        <v>41</v>
+      </c>
+      <c r="H17" t="s">
+        <v>26</v>
+      </c>
+      <c r="I17" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
